--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702419</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127701885</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702419</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127701885</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702419</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127701885</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128341510</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577922</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7078251</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,6 +993,448 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128439553</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577901</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7078281</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128447991</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577876</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7078322</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färsk Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128439771</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577891</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7078292</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färsk Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128439544</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577914</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7078281</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färsk Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702419</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128341510</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702419</v>
       </c>
       <c r="B2" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127701885</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128341510</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>128439553</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128447991</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>128439771</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128439544</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,7 +892,7 @@
         <v>128341510</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128439553</v>
+        <v>128447991</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,19 +1023,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1049,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577901</v>
+        <v>577876</v>
       </c>
       <c r="R5" t="n">
-        <v>7078281</v>
+        <v>7078322</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,6 +1076,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färsk Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128447991</v>
+        <v>128439771</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577876</v>
+        <v>577891</v>
       </c>
       <c r="R6" t="n">
-        <v>7078322</v>
+        <v>7078292</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1223,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128439771</v>
+        <v>128439544</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,26 +1248,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577891</v>
+        <v>577914</v>
       </c>
       <c r="R7" t="n">
-        <v>7078292</v>
+        <v>7078281</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1335,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128439544</v>
+        <v>128691852</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577914</v>
+        <v>577957</v>
       </c>
       <c r="R8" t="n">
-        <v>7078281</v>
+        <v>7078318</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1400,17 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färsk Ringhack</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,6 +1415,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128692179</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577925</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7078282</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1324,7 +1324,7 @@
         <v>128691852</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128691852</v>
+        <v>128692179</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577957</v>
+        <v>577925</v>
       </c>
       <c r="R8" t="n">
-        <v>7078318</v>
+        <v>7078282</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1415,103 +1415,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128692179</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57849</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>577925</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7078282</v>
-      </c>
-      <c r="S9" t="n">
-        <v>15</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Michaela Ehmann</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Michaela Ehmann</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1324,7 +1324,7 @@
         <v>128692179</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128341510</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>128447991</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128439771</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128439544</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1324,7 +1324,7 @@
         <v>128692179</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128341510</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>128447991</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128439771</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128439544</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -998,7 +998,7 @@
         <v>128447991</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128439771</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128439544</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>128692179</v>
       </c>
       <c r="B8" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1324,7 +1324,7 @@
         <v>128692179</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1416,6 +1416,297 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129293110</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577913</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7078254</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129294081</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577905</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7078287</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129293742</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577910</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7078255</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1418,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129293110</v>
+        <v>129294081</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577913</v>
+        <v>577905</v>
       </c>
       <c r="R9" t="n">
-        <v>7078254</v>
+        <v>7078287</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129294081</v>
+        <v>129293110</v>
       </c>
       <c r="B10" t="n">
         <v>79039</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577905</v>
+        <v>577913</v>
       </c>
       <c r="R10" t="n">
-        <v>7078287</v>
+        <v>7078254</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129294081</v>
+        <v>129293110</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577905</v>
+        <v>577913</v>
       </c>
       <c r="R9" t="n">
-        <v>7078287</v>
+        <v>7078254</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129293110</v>
+        <v>129294081</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577913</v>
+        <v>577905</v>
       </c>
       <c r="R10" t="n">
-        <v>7078254</v>
+        <v>7078287</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1615,7 +1615,7 @@
         <v>129293742</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1418,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129293110</v>
+        <v>129294081</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577913</v>
+        <v>577905</v>
       </c>
       <c r="R9" t="n">
-        <v>7078254</v>
+        <v>7078287</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129294081</v>
+        <v>129293110</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577905</v>
+        <v>577913</v>
       </c>
       <c r="R10" t="n">
-        <v>7078287</v>
+        <v>7078254</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1418,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129294081</v>
+        <v>129293110</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577905</v>
+        <v>577913</v>
       </c>
       <c r="R9" t="n">
-        <v>7078287</v>
+        <v>7078254</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129293110</v>
+        <v>129294081</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577913</v>
+        <v>577905</v>
       </c>
       <c r="R10" t="n">
-        <v>7078254</v>
+        <v>7078287</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1421,7 +1421,7 @@
         <v>129293110</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>129294081</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129293742</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1421,7 +1421,7 @@
         <v>129293110</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>129294081</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129293742</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1418,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129293110</v>
+        <v>129294081</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577913</v>
+        <v>577905</v>
       </c>
       <c r="R9" t="n">
-        <v>7078254</v>
+        <v>7078287</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129294081</v>
+        <v>129293110</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577905</v>
+        <v>577913</v>
       </c>
       <c r="R10" t="n">
-        <v>7078287</v>
+        <v>7078254</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1418,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129294081</v>
+        <v>129293110</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577905</v>
+        <v>577913</v>
       </c>
       <c r="R9" t="n">
-        <v>7078287</v>
+        <v>7078254</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129293110</v>
+        <v>129294081</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577913</v>
+        <v>577905</v>
       </c>
       <c r="R10" t="n">
-        <v>7078254</v>
+        <v>7078287</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1421,7 +1421,7 @@
         <v>129294081</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>129293110</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129293742</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129294081</v>
+        <v>129293110</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577905</v>
+        <v>577913</v>
       </c>
       <c r="R9" t="n">
-        <v>7078287</v>
+        <v>7078254</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129293110</v>
+        <v>129294081</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577913</v>
+        <v>577905</v>
       </c>
       <c r="R10" t="n">
-        <v>7078254</v>
+        <v>7078287</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1615,7 +1615,7 @@
         <v>129293742</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -1421,7 +1421,7 @@
         <v>129293110</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>129294081</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>129293742</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,6 +1707,122 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128439553</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577901</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7078281</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127702419</v>
+        <v>129293038</v>
       </c>
       <c r="B2" t="n">
-        <v>57844</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577847</v>
+        <v>577907</v>
       </c>
       <c r="R2" t="n">
-        <v>7078458</v>
+        <v>7078220</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,65 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127701885</v>
+        <v>129293110</v>
       </c>
       <c r="B3" t="n">
-        <v>56875</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577865</v>
+        <v>577913</v>
       </c>
       <c r="R3" t="n">
-        <v>7078357</v>
+        <v>7078254</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128341510</v>
+        <v>129293702</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+          <t>Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577922</v>
+        <v>577898</v>
       </c>
       <c r="R4" t="n">
-        <v>7078251</v>
+        <v>7078252</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -963,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,55 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128447991</v>
+        <v>129293742</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577876</v>
+        <v>577910</v>
       </c>
       <c r="R5" t="n">
-        <v>7078322</v>
+        <v>7078255</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1070,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk Ringhack</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,55 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128439771</v>
+        <v>129294081</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577891</v>
+        <v>577905</v>
       </c>
       <c r="R6" t="n">
-        <v>7078292</v>
+        <v>7078287</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1182,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk Ringhack</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,7 +1163,7 @@
         <v>128439544</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128692179</v>
+        <v>128439553</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,34 +1273,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577925</v>
+        <v>577901</v>
       </c>
       <c r="R8" t="n">
-        <v>7078282</v>
+        <v>7078281</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129293110</v>
+        <v>128439771</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,34 +1389,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577913</v>
+        <v>577891</v>
       </c>
       <c r="R9" t="n">
-        <v>7078254</v>
+        <v>7078292</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,12 +1453,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färsk Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129294081</v>
+        <v>128447991</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,34 +1501,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577905</v>
+        <v>577876</v>
       </c>
       <c r="R10" t="n">
-        <v>7078287</v>
+        <v>7078322</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,12 +1565,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färsk Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,45 +1602,65 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129293742</v>
+        <v>127701885</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577910</v>
+        <v>577865</v>
       </c>
       <c r="R11" t="n">
-        <v>7078255</v>
+        <v>7078357</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,12 +1687,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128439553</v>
+        <v>127702419</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,53 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577901</v>
+        <v>577847</v>
       </c>
       <c r="R12" t="n">
-        <v>7078281</v>
+        <v>7078458</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1793,12 +1784,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,6 +1813,302 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128341510</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577922</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7078251</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128692179</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577925</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7078282</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127702083</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Backe (Tågsjön), Backe (Tågsjön), Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577900</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7078426</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39095-2025 artfynd.xlsx
+++ b/artfynd/A 39095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293110</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293702</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293742</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294081</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439544</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439553</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128439771</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128447991</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701885</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702419</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341510</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2016,6 +2081,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128692179</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2109,8 +2179,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>